--- a/request_forms/049_patient_record_lookup_form--request_forms.xlsx
+++ b/request_forms/049_patient_record_lookup_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'abc_medical_group'}</t>
+          <t>abc_medical_group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'ABC Medical Group'}</t>
+          <t>ABC Medical Group</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'def_medical_group'}</t>
+          <t>def_medical_group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'DEF Medical Group'}</t>
+          <t>DEF Medical Group</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'ghi_medical_group'}</t>
+          <t>ghi_medical_group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'GHI Medical Group'}</t>
+          <t>GHI Medical Group</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'general_medicine'}</t>
+          <t>general_medicine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'General Medicine'}</t>
+          <t>General Medicine</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'general_surgery'}</t>
+          <t>general_surgery</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'General Surgery'}</t>
+          <t>General Surgery</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'general_surgery_(pediatrics)'}</t>
+          <t>general_surgery_(pediatrics)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'General Surgery (Pediatrics)'}</t>
+          <t>General Surgery (Pediatrics)</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
